--- a/multifunctionality/Tables/20260415_MF_ES_Summary_Score.xlsx
+++ b/multifunctionality/Tables/20260415_MF_ES_Summary_Score.xlsx
@@ -1,289 +1,296 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baldo\Documents\GitHub\RESONATE_WP4\multifunctionality\Tables\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13BD415E-F691-4CB5-9D36-EEB89FAAED67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="20260415_MF_ES_Summary_Score" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="20260415_MF_ES_Summary_Score" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
-  <si>
-    <t xml:space="preserve">rcp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mgm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Climate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Biodiversity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rcp45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAPTATION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.51 (0.44–0.59)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.84 (0.78–0.88)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60 (0.55–0.64)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.70 (0.68–0.72)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65 (2.49–2.73)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.53 (0.41–0.62)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86 (0.80–0.91)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.63 (0.56–0.67)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62 (0.60–0.65)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64 (2.44–2.74)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BIOECONOMY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.57 (0.48–0.64)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.63 (0.57–0.67)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60 (0.58–0.63)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64 (2.46–2.73)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONSERVATION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54 (0.40–0.66)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.73 (0.68–0.76)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.67 (0.58–0.72)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.74 (0.71–0.79)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68 (2.47–2.81)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNMANAGED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.75 (0.55–0.92)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42 (0.39–0.43)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81 (0.70–0.89)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.82 (0.76–0.89)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80 (2.55–2.99)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rcp85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49 (0.39–0.57)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86 (0.76–0.96)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61 (0.51–0.71)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.70 (0.67–0.76)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65 (2.54–2.89)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48 (0.36–0.60)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88 (0.77–1.00)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.63 (0.51–0.73)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.63 (0.58–0.71)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62 (2.41–2.89)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.53 (0.42–0.63)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86 (0.75–0.96)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.63 (0.51–0.75)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61 (0.56–0.69)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63 (2.48–2.89)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.51 (0.39–0.67)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.74 (0.65–0.82)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.67 (0.53–0.80)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.75 (0.69–0.85)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67 (2.45–2.97)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69 (0.46–0.98)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42 (0.40–0.45)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81 (0.59–1.00)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.84 (0.75–0.99)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76 (2.45–3.16)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">refclim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.51 (0.49–0.53)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89 (0.89–0.90)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.65 (0.65–0.66)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.67 (0.67–0.68)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72 (2.70–2.75)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.57 (0.55–0.61)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.90 (0.90–0.90)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.68 (0.68–0.69)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.57 (0.57–0.58)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73 (2.70–2.76)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.59 (0.56–0.61)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69 (0.69–0.70)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56 (0.55–0.56)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73 (2.70–2.74)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.58 (0.53–0.62)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.76 (0.76–0.76)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.75 (0.74–0.77)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.70 (0.69–0.70)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78 (2.75–2.83)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85 (0.78–0.93)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42 (0.42–0.43)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95 (0.93–0.97)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.76 (0.74–0.78)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98 (2.91–3.05)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="88">
+  <si>
+    <t>rcp</t>
+  </si>
+  <si>
+    <t>mgm</t>
+  </si>
+  <si>
+    <t>Climate</t>
+  </si>
+  <si>
+    <t>Production</t>
+  </si>
+  <si>
+    <t>Water</t>
+  </si>
+  <si>
+    <t>Biodiversity</t>
+  </si>
+  <si>
+    <t>score</t>
+  </si>
+  <si>
+    <t>rcp45</t>
+  </si>
+  <si>
+    <t>ADAPTATION</t>
+  </si>
+  <si>
+    <t>0.51 (0.44–0.59)</t>
+  </si>
+  <si>
+    <t>0.84 (0.78–0.88)</t>
+  </si>
+  <si>
+    <t>0.60 (0.55–0.64)</t>
+  </si>
+  <si>
+    <t>0.70 (0.68–0.72)</t>
+  </si>
+  <si>
+    <t>2.65 (2.49–2.73)</t>
+  </si>
+  <si>
+    <t>BAU</t>
+  </si>
+  <si>
+    <t>0.53 (0.41–0.62)</t>
+  </si>
+  <si>
+    <t>0.86 (0.80–0.91)</t>
+  </si>
+  <si>
+    <t>0.63 (0.56–0.67)</t>
+  </si>
+  <si>
+    <t>0.62 (0.60–0.65)</t>
+  </si>
+  <si>
+    <t>2.64 (2.44–2.74)</t>
+  </si>
+  <si>
+    <t>BIOECONOMY</t>
+  </si>
+  <si>
+    <t>0.57 (0.48–0.64)</t>
+  </si>
+  <si>
+    <t>0.63 (0.57–0.67)</t>
+  </si>
+  <si>
+    <t>0.60 (0.58–0.63)</t>
+  </si>
+  <si>
+    <t>2.64 (2.46–2.73)</t>
+  </si>
+  <si>
+    <t>CONSERVATION</t>
+  </si>
+  <si>
+    <t>0.54 (0.40–0.66)</t>
+  </si>
+  <si>
+    <t>0.73 (0.68–0.76)</t>
+  </si>
+  <si>
+    <t>0.67 (0.58–0.72)</t>
+  </si>
+  <si>
+    <t>0.74 (0.71–0.79)</t>
+  </si>
+  <si>
+    <t>2.68 (2.47–2.81)</t>
+  </si>
+  <si>
+    <t>UNMANAGED</t>
+  </si>
+  <si>
+    <t>0.75 (0.55–0.92)</t>
+  </si>
+  <si>
+    <t>0.42 (0.39–0.43)</t>
+  </si>
+  <si>
+    <t>0.81 (0.70–0.89)</t>
+  </si>
+  <si>
+    <t>0.82 (0.76–0.89)</t>
+  </si>
+  <si>
+    <t>2.80 (2.55–2.99)</t>
+  </si>
+  <si>
+    <t>rcp85</t>
+  </si>
+  <si>
+    <t>0.49 (0.39–0.57)</t>
+  </si>
+  <si>
+    <t>0.86 (0.76–0.96)</t>
+  </si>
+  <si>
+    <t>0.61 (0.51–0.71)</t>
+  </si>
+  <si>
+    <t>0.70 (0.67–0.76)</t>
+  </si>
+  <si>
+    <t>2.65 (2.54–2.89)</t>
+  </si>
+  <si>
+    <t>0.48 (0.36–0.60)</t>
+  </si>
+  <si>
+    <t>0.88 (0.77–1.00)</t>
+  </si>
+  <si>
+    <t>0.63 (0.51–0.73)</t>
+  </si>
+  <si>
+    <t>0.63 (0.58–0.71)</t>
+  </si>
+  <si>
+    <t>2.62 (2.41–2.89)</t>
+  </si>
+  <si>
+    <t>0.53 (0.42–0.63)</t>
+  </si>
+  <si>
+    <t>0.86 (0.75–0.96)</t>
+  </si>
+  <si>
+    <t>0.63 (0.51–0.75)</t>
+  </si>
+  <si>
+    <t>0.61 (0.56–0.69)</t>
+  </si>
+  <si>
+    <t>2.63 (2.48–2.89)</t>
+  </si>
+  <si>
+    <t>0.51 (0.39–0.67)</t>
+  </si>
+  <si>
+    <t>0.74 (0.65–0.82)</t>
+  </si>
+  <si>
+    <t>0.67 (0.53–0.80)</t>
+  </si>
+  <si>
+    <t>0.75 (0.69–0.85)</t>
+  </si>
+  <si>
+    <t>2.67 (2.45–2.97)</t>
+  </si>
+  <si>
+    <t>0.69 (0.46–0.98)</t>
+  </si>
+  <si>
+    <t>0.42 (0.40–0.45)</t>
+  </si>
+  <si>
+    <t>0.81 (0.59–1.00)</t>
+  </si>
+  <si>
+    <t>0.84 (0.75–0.99)</t>
+  </si>
+  <si>
+    <t>2.76 (2.45–3.16)</t>
+  </si>
+  <si>
+    <t>refclim</t>
+  </si>
+  <si>
+    <t>0.51 (0.49–0.53)</t>
+  </si>
+  <si>
+    <t>0.89 (0.89–0.90)</t>
+  </si>
+  <si>
+    <t>0.65 (0.65–0.66)</t>
+  </si>
+  <si>
+    <t>0.67 (0.67–0.68)</t>
+  </si>
+  <si>
+    <t>2.72 (2.70–2.75)</t>
+  </si>
+  <si>
+    <t>0.57 (0.55–0.61)</t>
+  </si>
+  <si>
+    <t>0.90 (0.90–0.90)</t>
+  </si>
+  <si>
+    <t>0.68 (0.68–0.69)</t>
+  </si>
+  <si>
+    <t>0.57 (0.57–0.58)</t>
+  </si>
+  <si>
+    <t>2.73 (2.70–2.76)</t>
+  </si>
+  <si>
+    <t>0.59 (0.56–0.61)</t>
+  </si>
+  <si>
+    <t>0.69 (0.69–0.70)</t>
+  </si>
+  <si>
+    <t>0.56 (0.55–0.56)</t>
+  </si>
+  <si>
+    <t>2.73 (2.70–2.74)</t>
+  </si>
+  <si>
+    <t>0.58 (0.53–0.62)</t>
+  </si>
+  <si>
+    <t>0.76 (0.76–0.76)</t>
+  </si>
+  <si>
+    <t>0.75 (0.74–0.77)</t>
+  </si>
+  <si>
+    <t>0.70 (0.69–0.70)</t>
+  </si>
+  <si>
+    <t>2.78 (2.75–2.83)</t>
+  </si>
+  <si>
+    <t>0.85 (0.78–0.93)</t>
+  </si>
+  <si>
+    <t>0.42 (0.42–0.43)</t>
+  </si>
+  <si>
+    <t>0.95 (0.93–0.97)</t>
+  </si>
+  <si>
+    <t>0.76 (0.74–0.78)</t>
+  </si>
+  <si>
+    <t>2.98 (2.91–3.05)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -319,6 +326,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -600,11 +616,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -627,7 +647,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -650,7 +670,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -673,7 +693,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -696,7 +716,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -719,7 +739,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -742,7 +762,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -765,7 +785,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>37</v>
       </c>
@@ -788,7 +808,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -811,7 +831,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -834,7 +854,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -857,7 +877,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -880,7 +900,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>63</v>
       </c>
@@ -903,7 +923,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>63</v>
       </c>
@@ -926,7 +946,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>63</v>
       </c>
@@ -949,7 +969,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>63</v>
       </c>
@@ -974,6 +994,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>